--- a/templates/SIB_QR_Report_Template.xlsx
+++ b/templates/SIB_QR_Report_Template.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310"/>
   </bookViews>
   <sheets>
-    <sheet name="QR Collection" sheetId="1" r:id="rId1"/>
+    <sheet name="QR Reports Template" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
